--- a/artfynd/A 23498-2023 artfynd.xlsx
+++ b/artfynd/A 23498-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23498-2023 artfynd.xlsx
+++ b/artfynd/A 23498-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99329664</v>
+        <v>99369091</v>
       </c>
       <c r="B2" t="n">
-        <v>55978</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102966</v>
+        <v>100065</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Larus argentatus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pontoppidan, 1763</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>FM-19555-4-27, Upl</t>
+          <t>FM-9-2-28, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>674839.329089281</v>
+        <v>674824</v>
       </c>
       <c r="R2" t="n">
-        <v>6697488.615308507</v>
+        <v>6697533</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,22 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2007-06-18</t>
+          <t>2018-06-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2007-06-18</t>
+          <t>2018-06-01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,42 +790,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99329667</v>
+        <v>99329664</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>102966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Larus argentatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Pontoppidan, 1763</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>674839.329089281</v>
+        <v>674840</v>
       </c>
       <c r="R3" t="n">
-        <v>6697488.615308507</v>
+        <v>6697488</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,32 +905,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99366914</v>
+        <v>99366923</v>
       </c>
       <c r="B4" t="n">
-        <v>57007</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103042</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -959,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>674806.6841248561</v>
+        <v>674806</v>
       </c>
       <c r="R4" t="n">
-        <v>6697641.080584639</v>
+        <v>6697641</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,22 +974,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-06-01</t>
+          <t>2013-05-30</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>04:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-06-01</t>
+          <t>2013-05-30</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>04:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,37 +1020,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99369098</v>
+        <v>99368903</v>
       </c>
       <c r="B5" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>103018</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1075,14 +1055,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>FM-9-2-28, Upl</t>
+          <t>FM-9356-4-14, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>674823.7751536559</v>
+        <v>674808</v>
       </c>
       <c r="R5" t="n">
-        <v>6697533.434223384</v>
+        <v>6697605</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1107,24 +1087,25 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2013-05-30</t>
+          <t>2003-05-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>04:28</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2013-05-30</t>
+          <t>2003-05-27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>04:28</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,15 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99368903</v>
+        <v>99329667</v>
       </c>
       <c r="B6" t="n">
-        <v>56859</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,21 +1147,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103018</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1195,14 +1171,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>FM-9356-4-14, Upl</t>
+          <t>FM-19555-4-27, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>674807.9264085086</v>
+        <v>674840</v>
       </c>
       <c r="R6" t="n">
-        <v>6697604.984278814</v>
+        <v>6697488</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,25 +1203,24 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2003-05-27</t>
+          <t>2007-06-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2003-05-27</t>
+          <t>2007-06-18</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,6 +1244,583 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>99328520</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>FM-20115-3-75, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>674776</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6697602</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2018-06-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2018-06-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>99366914</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>FM-5-5-24, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>674806</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6697641</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2018-06-01</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2018-06-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>99368640</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>FM-9431-5-18, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>674797</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6697623</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2002-05-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2002-05-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>99368902</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>FM-9356-4-14, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>674808</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6697605</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2003-05-27</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2003-05-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>99369098</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>FM-9-2-28, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>674824</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6697533</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2013-05-30</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>04:28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2013-05-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>04:28</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Forsmark platsundersökning</t>
         </is>

--- a/artfynd/A 23498-2023 artfynd.xlsx
+++ b/artfynd/A 23498-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99369091</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99329664</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99366923</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1133,6 +1153,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99368903</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1248,6 +1273,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99329667</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1363,6 +1393,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99328520</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1478,6 +1513,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99366914</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1594,6 +1634,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99368640</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1710,6 +1755,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99368902</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1825,8 +1875,25 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99369098</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>